--- a/sgturnos/mallas/malla_aux01_2026-01.xlsx
+++ b/sgturnos/mallas/malla_aux01_2026-01.xlsx
@@ -125,15 +125,15 @@
     <t>CP3h+AP9h</t>
   </si>
   <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
     <t>LB</t>
   </si>
   <si>
-    <t>TN</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
@@ -146,10 +146,10 @@
     <t>Victor Guerrero</t>
   </si>
   <si>
+    <t>Pedro Sanchez</t>
+  </si>
+  <si>
     <t>AP12h</t>
-  </si>
-  <si>
-    <t>Pedro Sanchez</t>
   </si>
   <si>
     <t>Isabel Muñoz</t>
@@ -473,89 +473,89 @@
       <c r="D2" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E2" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="G2" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="H2" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="I2" t="s" s="4">
-        <v>37</v>
+      <c r="E2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="G2" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="L2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="L2" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="M2" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="N2" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s" s="1">
         <v>35</v>
       </c>
       <c r="P2" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q2" t="s" s="1">
         <v>35</v>
       </c>
       <c r="R2" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T2" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V2" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W2" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X2" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Y2" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z2" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB2" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC2" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD2" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AE2" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AF2" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="AF2" t="s" s="2">
+        <v>37</v>
       </c>
       <c r="AG2" t="s" s="0">
         <v>40</v>
@@ -577,89 +577,89 @@
       <c r="D3" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="G3" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="H3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s" s="5">
-        <v>39</v>
+      <c r="E3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="G3" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I3" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M3" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="O3" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="P3" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="O3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="Q3" t="s" s="1">
         <v>35</v>
       </c>
       <c r="R3" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T3" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="U3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V3" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="U3" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="V3" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="W3" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X3" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Y3" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z3" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AA3" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AB3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC3" t="s" s="5">
+      <c r="AA3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB3" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AC3" t="s" s="4">
         <v>39</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AE3" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AF3" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="AF3" t="s" s="2">
+        <v>37</v>
       </c>
       <c r="AG3" t="s" s="0">
         <v>40</v>
@@ -681,88 +681,88 @@
       <c r="D4" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E4" t="s" s="3">
-        <v>44</v>
+      <c r="E4" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s" s="1">
         <v>35</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N4" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="O4" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="P4" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="O4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="P4" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="Q4" t="s" s="1">
         <v>35</v>
       </c>
       <c r="R4" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="U4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V4" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="U4" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="V4" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="W4" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X4" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Y4" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z4" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AA4" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AB4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC4" t="s" s="5">
+      <c r="AA4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB4" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AC4" t="s" s="4">
         <v>39</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AE4" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AF4" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="AF4" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AG4" t="s" s="0">
@@ -774,7 +774,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s" s="1">
         <v>35</v>
@@ -786,88 +786,88 @@
         <v>35</v>
       </c>
       <c r="E5" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s" s="1">
         <v>35</v>
       </c>
       <c r="L5" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M5" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="N5" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="P5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Q5" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="R5" t="s" s="4">
-        <v>37</v>
+      <c r="N5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="P5" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R5" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T5" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V5" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="U5" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="V5" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="W5" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X5" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Y5" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z5" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AA5" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC5" t="s" s="5">
+      <c r="AA5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB5" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AC5" t="s" s="4">
         <v>39</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AE5" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG5" t="s" s="0">
         <v>40</v>
@@ -890,88 +890,88 @@
         <v>35</v>
       </c>
       <c r="E6" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K6" t="s" s="1">
         <v>35</v>
       </c>
       <c r="L6" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M6" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="N6" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="P6" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Q6" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="R6" t="s" s="4">
-        <v>37</v>
+      <c r="N6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="O6" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="P6" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R6" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T6" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="U6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V6" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="U6" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="V6" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="W6" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X6" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Y6" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z6" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AA6" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC6" t="s" s="5">
+      <c r="AA6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AB6" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AC6" t="s" s="4">
         <v>39</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AE6" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AF6" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG6" t="s" s="0">
         <v>40</v>
@@ -991,91 +991,91 @@
         <v>36</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="G7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="I7" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="K7" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="L7" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M7" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="N7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="O7" t="s" s="1">
-        <v>35</v>
+      <c r="N7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="O7" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="P7" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q7" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R7" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="S7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T7" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="U7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="V7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="W7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X7" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="S7" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="T7" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V7" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="W7" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="X7" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="Y7" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z7" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AA7" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AB7" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AC7" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC7" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AE7" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>38</v>
+        <v>38</v>
+      </c>
+      <c r="AF7" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="AG7" t="s" s="0">
         <v>40</v>
@@ -1095,91 +1095,91 @@
         <v>36</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="I8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="K8" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="J8" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="L8" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M8" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="N8" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="O8" t="s" s="1">
-        <v>35</v>
+      <c r="N8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="O8" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="P8" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q8" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="S8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="U8" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="V8" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Y8" t="s" s="4">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="S8" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="T8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V8" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="W8" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y8" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="Z8" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AA8" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AB8" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AC8" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE8" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC8" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AD8" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AE8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AF8" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="AG8" t="s" s="0">
         <v>40</v>
@@ -1199,91 +1199,91 @@
         <v>36</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s" s="4">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="H9" t="s" s="3">
+        <v>45</v>
       </c>
       <c r="I9" t="s" s="1">
         <v>35</v>
       </c>
       <c r="J9" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K9" t="s" s="1">
         <v>35</v>
       </c>
       <c r="L9" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="N9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O9" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="M9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="O9" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="P9" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q9" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="T9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="U9" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="V9" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="S9" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="T9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V9" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="W9" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="X9" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Y9" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AA9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AB9" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AC9" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE9" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Y9" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="Z9" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AA9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC9" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AD9" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AE9" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AF9" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="AG9" t="s" s="0">
         <v>40</v>
@@ -1297,97 +1297,97 @@
         <v>50</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F10" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="G10" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="H10" t="s" s="4">
-        <v>37</v>
+      <c r="E10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="G10" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="H10" t="s" s="3">
+        <v>45</v>
       </c>
       <c r="I10" t="s" s="1">
         <v>35</v>
       </c>
       <c r="J10" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="K10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="L10" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="K10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="L10" t="s" s="4">
         <v>39</v>
       </c>
       <c r="M10" t="s" s="1">
         <v>35</v>
       </c>
       <c r="N10" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P10" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q10" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R10" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S10" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T10" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="U10" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="V10" t="s" s="1">
-        <v>35</v>
+      <c r="U10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V10" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="W10" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y10" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AA10" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AB10" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AC10" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE10" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>38</v>
+        <v>38</v>
+      </c>
+      <c r="Z10" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AA10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC10" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AD10" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AE10" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AF10" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="AG10" t="s" s="0">
         <v>40</v>
@@ -1401,97 +1401,97 @@
         <v>51</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E11" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F11" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="G11" t="s" s="1">
-        <v>35</v>
+      <c r="E11" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="H11" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s" s="1">
         <v>35</v>
       </c>
       <c r="J11" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L11" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="M11" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="N11" t="s" s="4">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="M11" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="N11" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P11" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Q11" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="R11" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="Q11" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="R11" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="S11" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T11" t="s" s="1">
         <v>35</v>
       </c>
       <c r="U11" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V11" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="W11" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y11" t="s" s="5">
+      <c r="W11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X11" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="Y11" t="s" s="4">
         <v>39</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA11" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AB11" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AC11" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC11" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AD11" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AE11" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AF11" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG11" t="s" s="0">
         <v>40</v>
@@ -1505,97 +1505,97 @@
         <v>52</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F12" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s" s="6">
         <v>36</v>
       </c>
+      <c r="E12" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s" s="3">
+        <v>45</v>
+      </c>
       <c r="G12" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="H12" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="I12" t="s" s="1">
-        <v>35</v>
+      <c r="H12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="J12" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L12" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="N12" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O12" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P12" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Q12" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="R12" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="M12" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="N12" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="P12" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="Q12" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="R12" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="S12" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T12" t="s" s="1">
         <v>35</v>
       </c>
       <c r="U12" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V12" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="W12" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Y12" t="s" s="5">
+      <c r="W12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X12" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="Y12" t="s" s="4">
         <v>39</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA12" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AB12" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AC12" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC12" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AD12" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AE12" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AF12" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG12" t="s" s="0">
         <v>40</v>
@@ -1609,97 +1609,97 @@
         <v>53</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E13" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F13" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s" s="6">
         <v>36</v>
       </c>
+      <c r="E13" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s" s="3">
+        <v>45</v>
+      </c>
       <c r="G13" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="H13" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="I13" t="s" s="1">
-        <v>35</v>
+      <c r="H13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="I13" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="J13" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L13" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="N13" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O13" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P13" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="M13" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="N13" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="P13" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="Q13" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R13" t="s" s="1">
         <v>35</v>
       </c>
       <c r="S13" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U13" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="T13" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="U13" t="s" s="4">
         <v>39</v>
       </c>
       <c r="V13" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="W13" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="X13" t="s" s="1">
-        <v>35</v>
+      <c r="W13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X13" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="Y13" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA13" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC13" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AD13" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE13" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="AB13" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AC13" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE13" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AF13" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG13" t="s" s="0">
         <v>40</v>
@@ -1713,97 +1713,97 @@
         <v>54</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E14" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="F14" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s" s="6">
         <v>36</v>
       </c>
+      <c r="E14" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s" s="3">
+        <v>45</v>
+      </c>
       <c r="G14" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="H14" t="s" s="3">
-        <v>44</v>
+      <c r="H14" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="I14" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="J14" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="L14" t="s" s="5">
+      <c r="J14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K14" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="L14" t="s" s="4">
         <v>39</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N14" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O14" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P14" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="P14" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="Q14" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R14" t="s" s="1">
         <v>35</v>
       </c>
       <c r="S14" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U14" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="T14" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="U14" t="s" s="4">
         <v>39</v>
       </c>
       <c r="V14" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="W14" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="X14" t="s" s="1">
-        <v>35</v>
+      <c r="W14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="X14" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="Y14" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA14" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC14" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AD14" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE14" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="AB14" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AC14" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE14" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AF14" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG14" t="s" s="0">
         <v>40</v>
@@ -1817,10 +1817,10 @@
         <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s" s="6">
         <v>36</v>
@@ -1828,86 +1828,86 @@
       <c r="E15" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="F15" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="G15" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="H15" t="s" s="3">
-        <v>44</v>
+      <c r="F15" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="G15" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="I15" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="J15" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="K15" t="s" s="1">
-        <v>35</v>
+      <c r="J15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K15" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="L15" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N15" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P15" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q15" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R15" t="s" s="1">
         <v>35</v>
       </c>
       <c r="S15" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="T15" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="U15" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W15" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U15" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="V15" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="W15" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y15" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z15" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA15" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AB15" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC15" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AD15" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE15" t="s" s="1">
-        <v>35</v>
+      <c r="AB15" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AC15" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE15" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AF15" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG15" t="s" s="0">
         <v>40</v>
@@ -1921,10 +1921,10 @@
         <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s" s="6">
         <v>36</v>
@@ -1932,85 +1932,85 @@
       <c r="E16" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="F16" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="G16" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="H16" t="s" s="3">
-        <v>44</v>
+      <c r="F16" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="H16" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="I16" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="J16" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="K16" t="s" s="1">
-        <v>35</v>
+      <c r="J16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="K16" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="L16" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N16" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="P16" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Q16" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="R16" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="O16" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="P16" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R16" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="S16" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="T16" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="U16" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W16" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U16" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="V16" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="W16" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y16" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z16" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA16" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AB16" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC16" t="s" s="5">
-        <v>39</v>
+      <c r="AB16" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AC16" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AD16" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AE16" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AF16" t="s" s="4">
+      <c r="AF16" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AG16" t="s" s="0">
@@ -2025,10 +2025,10 @@
         <v>57</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s" s="6">
         <v>36</v>
@@ -2036,86 +2036,86 @@
       <c r="E17" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="F17" t="s" s="3">
-        <v>44</v>
+      <c r="F17" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="G17" t="s" s="1">
         <v>35</v>
       </c>
       <c r="H17" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J17" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K17" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="L17" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="N17" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="P17" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Q17" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="R17" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L17" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="M17" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="N17" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="O17" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="P17" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="R17" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="S17" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="T17" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="U17" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W17" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U17" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="V17" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="W17" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y17" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z17" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA17" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AB17" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AC17" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AD17" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF17" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="AE17" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>37</v>
       </c>
       <c r="AG17" t="s" s="0">
         <v>40</v>
@@ -2134,92 +2134,92 @@
       <c r="C18" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D18" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="E18" t="s" s="1">
-        <v>35</v>
+      <c r="D18" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="G18" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H18" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="G18" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="H18" t="s" s="4">
         <v>39</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J18" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K18" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="L18" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="N18" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="P18" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L18" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="M18" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="N18" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="O18" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="P18" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="Q18" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R18" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="S18" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="T18" t="s" s="1">
-        <v>35</v>
+      <c r="S18" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T18" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="U18" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W18" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y18" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z18" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA18" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AB18" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AC18" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AD18" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF18" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="AE18" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>37</v>
       </c>
       <c r="AG18" t="s" s="0">
         <v>40</v>
@@ -2238,92 +2238,92 @@
       <c r="C19" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D19" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="E19" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="F19" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H19" t="s" s="5">
+      <c r="D19" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="F19" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="G19" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s" s="4">
         <v>39</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J19" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K19" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L19" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L19" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="M19" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N19" t="s" s="1">
         <v>35</v>
       </c>
       <c r="O19" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P19" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q19" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="P19" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q19" t="s" s="4">
         <v>39</v>
       </c>
       <c r="R19" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="S19" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="T19" t="s" s="1">
-        <v>35</v>
+      <c r="S19" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T19" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="U19" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W19" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y19" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z19" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA19" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AB19" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AC19" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AD19" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AF19" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG19" t="s" s="0">
         <v>40</v>
@@ -2342,92 +2342,92 @@
       <c r="C20" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D20" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="E20" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="F20" t="s" s="4">
-        <v>37</v>
+      <c r="D20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s" s="3">
+        <v>45</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J20" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K20" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L20" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="I20" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="J20" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L20" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="M20" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N20" t="s" s="1">
         <v>35</v>
       </c>
       <c r="O20" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q20" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="P20" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q20" t="s" s="4">
         <v>39</v>
       </c>
       <c r="R20" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="S20" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U20" t="s" s="5">
+      <c r="S20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="T20" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="U20" t="s" s="4">
         <v>39</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W20" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X20" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y20" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA20" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB20" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AC20" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AD20" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE20" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AF20" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF20" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AG20" t="s" s="0">
         <v>40</v>
@@ -2446,92 +2446,92 @@
       <c r="C21" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D21" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="E21" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="F21" t="s" s="4">
-        <v>37</v>
+      <c r="D21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s" s="3">
+        <v>45</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J21" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K21" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L21" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="I21" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="J21" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="L21" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="M21" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N21" t="s" s="1">
         <v>35</v>
       </c>
       <c r="O21" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q21" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="P21" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q21" t="s" s="4">
         <v>39</v>
       </c>
       <c r="R21" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S21" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="T21" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="U21" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W21" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U21" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="V21" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="W21" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="X21" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y21" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA21" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AB21" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AC21" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AD21" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AE21" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AF21" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AD21" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AE21" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AF21" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AG21" t="s" s="0">
         <v>40</v>
@@ -2550,92 +2550,92 @@
       <c r="C22" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="D22" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="E22" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="F22" t="s" s="4">
-        <v>37</v>
+      <c r="D22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="F22" t="s" s="3">
+        <v>45</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H22" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J22" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="I22" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="J22" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="K22" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L22" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="M22" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N22" t="s" s="1">
-        <v>35</v>
+      <c r="M22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="O22" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q22" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="P22" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q22" t="s" s="4">
         <v>39</v>
       </c>
       <c r="R22" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S22" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="T22" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="U22" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="W22" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="U22" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="V22" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="W22" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="X22" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y22" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="Z22" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AA22" t="s" s="1">
-        <v>35</v>
+      <c r="Z22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA22" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AB22" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD22" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF22" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="AE22" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AF22" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AG22" t="s" s="0">
         <v>40</v>
@@ -2655,88 +2655,88 @@
         <v>35</v>
       </c>
       <c r="D23" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="G23" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="H23" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J23" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K23" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="L23" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="M23" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N23" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H23" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="I23" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="J23" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="K23" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="L23" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="O23" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P23" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Q23" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R23" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S23" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U23" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V23" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W23" t="s" s="1">
         <v>35</v>
       </c>
       <c r="X23" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y23" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="Z23" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB23" t="s" s="5">
+      <c r="Z23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA23" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AB23" t="s" s="4">
         <v>39</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD23" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE23" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF23" t="s" s="1">
         <v>35</v>
@@ -2759,91 +2759,91 @@
         <v>35</v>
       </c>
       <c r="D24" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="G24" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="H24" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="J24" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="L24" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="M24" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N24" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H24" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="I24" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="J24" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="K24" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="L24" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="O24" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P24" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Q24" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="R24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S24" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="P24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q24" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="R24" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="S24" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U24" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V24" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W24" t="s" s="1">
         <v>35</v>
       </c>
       <c r="X24" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y24" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Z24" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB24" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD24" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AE24" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AF24" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="AA24" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC24" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AD24" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF24" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AG24" t="s" s="0">
         <v>40</v>
@@ -2863,88 +2863,88 @@
         <v>35</v>
       </c>
       <c r="D25" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H25" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I25" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J25" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="K25" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="L25" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="M25" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N25" t="s" s="1">
-        <v>35</v>
+      <c r="K25" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="L25" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="O25" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P25" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Q25" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="R25" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S25" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="P25" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q25" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="R25" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="S25" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U25" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V25" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W25" t="s" s="1">
         <v>35</v>
       </c>
       <c r="X25" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y25" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Z25" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB25" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD25" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE25" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF25" t="s" s="1">
         <v>35</v>
@@ -2964,91 +2964,91 @@
         <v>36</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="F26" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="G26" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="H26" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="E26" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H26" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="I26" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J26" t="s" s="1">
         <v>35</v>
       </c>
       <c r="K26" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="M26" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="N26" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="L26" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="N26" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="O26" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="P26" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Q26" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="R26" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S26" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U26" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="V26" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="W26" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="P26" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q26" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="R26" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="S26" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="T26" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="U26" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W26" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="X26" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y26" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Z26" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB26" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD26" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE26" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF26" t="s" s="1">
         <v>35</v>
@@ -3068,91 +3068,91 @@
         <v>36</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="F27" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="G27" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="H27" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="E27" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="F27" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H27" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="I27" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J27" t="s" s="1">
         <v>35</v>
       </c>
       <c r="K27" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="M27" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="L27" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M27" t="s" s="4">
         <v>39</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O27" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P27" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="Q27" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S27" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="U27" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="V27" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="W27" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q27" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="R27" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="S27" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="T27" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="U27" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W27" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="X27" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y27" t="s" s="1">
         <v>35</v>
       </c>
       <c r="Z27" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AB27" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD27" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE27" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF27" t="s" s="1">
         <v>35</v>
@@ -3172,94 +3172,94 @@
         <v>36</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D28" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="F28" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="G28" t="s" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="E28" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="G28" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="H28" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="I28" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="J28" t="s" s="1">
-        <v>35</v>
+      <c r="I28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J28" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="K28" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="M28" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="L28" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M28" t="s" s="4">
         <v>39</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O28" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P28" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Q28" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="R28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="S28" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q28" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="R28" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="S28" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="T28" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U28" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="V28" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="W28" t="s" s="1">
-        <v>35</v>
+      <c r="V28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W28" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="X28" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z28" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AA28" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AB28" t="s" s="4">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="AA28" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AB28" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD28" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF28" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="AE28" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AF28" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AG28" t="s" s="0">
         <v>40</v>
@@ -3276,94 +3276,94 @@
         <v>36</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="F29" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="G29" t="s" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="E29" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="F29" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="G29" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="H29" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="I29" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="J29" t="s" s="1">
-        <v>35</v>
+      <c r="I29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J29" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="K29" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="M29" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="L29" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="M29" t="s" s="4">
         <v>39</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O29" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P29" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Q29" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q29" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="R29" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S29" t="s" s="1">
         <v>35</v>
       </c>
       <c r="T29" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V29" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="W29" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="U29" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W29" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="X29" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z29" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AA29" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AB29" t="s" s="4">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="AA29" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AB29" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD29" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AF29" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="AE29" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AF29" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AG29" t="s" s="0">
         <v>40</v>
@@ -3380,94 +3380,94 @@
         <v>36</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="F30" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="G30" t="s" s="3">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="E30" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="G30" t="s" s="4">
+        <v>39</v>
       </c>
       <c r="H30" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="I30" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="J30" t="s" s="1">
-        <v>35</v>
+      <c r="I30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J30" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="K30" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M30" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="O30" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P30" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Q30" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="N30" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="O30" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Q30" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="R30" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S30" t="s" s="1">
         <v>35</v>
       </c>
       <c r="T30" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="V30" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="W30" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="U30" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="W30" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="X30" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z30" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB30" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="AA30" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AB30" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AC30" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD30" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AF30" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG30" t="s" s="0">
         <v>40</v>
@@ -3484,94 +3484,94 @@
         <v>36</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="G31" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H31" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="I31" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="J31" t="s" s="1">
-        <v>35</v>
+      <c r="G31" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="H31" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J31" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="K31" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L31" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="M31" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="O31" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="M31" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="N31" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="O31" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="P31" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q31" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R31" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S31" t="s" s="1">
         <v>35</v>
       </c>
       <c r="T31" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U31" t="s" s="1">
         <v>35</v>
       </c>
       <c r="V31" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X31" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z31" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA31" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AB31" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AC31" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD31" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AF31" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG31" t="s" s="0">
         <v>40</v>
@@ -3588,93 +3588,93 @@
         <v>36</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F32" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="H32" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="I32" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="J32" t="s" s="1">
-        <v>35</v>
+      <c r="G32" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="H32" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="J32" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="K32" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="L32" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="M32" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="O32" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P32" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q32" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="R32" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="S32" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="M32" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="N32" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="O32" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="P32" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q32" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="R32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S32" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="T32" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U32" t="s" s="1">
         <v>35</v>
       </c>
       <c r="V32" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X32" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z32" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA32" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AB32" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AC32" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD32" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AE32" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AF32" t="s" s="2">
+      <c r="AE32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF32" t="s" s="5">
         <v>38</v>
       </c>
       <c r="AG32" t="s" s="0">
@@ -3692,93 +3692,93 @@
         <v>36</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F33" t="s" s="1">
         <v>35</v>
       </c>
       <c r="G33" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H33" t="s" s="1">
         <v>35</v>
       </c>
       <c r="I33" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K33" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="L33" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="M33" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="O33" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P33" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q33" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="R33" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="S33" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="M33" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="N33" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="O33" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="P33" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q33" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="R33" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S33" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="T33" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U33" t="s" s="1">
         <v>35</v>
       </c>
       <c r="V33" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X33" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z33" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA33" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AB33" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AC33" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD33" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AE33" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AF33" t="s" s="2">
+      <c r="AE33" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF33" t="s" s="5">
         <v>38</v>
       </c>
       <c r="AG33" t="s" s="0">
@@ -3796,93 +3796,93 @@
         <v>36</v>
       </c>
       <c r="C34" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E34" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="F34" t="s" s="1">
-        <v>35</v>
+      <c r="E34" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F34" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="G34" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="I34" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="H34" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="I34" t="s" s="4">
         <v>39</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K34" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="L34" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="M34" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="O34" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="P34" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Q34" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="R34" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="S34" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="M34" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="N34" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="O34" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="P34" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q34" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="R34" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S34" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="T34" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="U34" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="V34" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V34" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X34" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="Z34" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="Y34" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="Z34" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="AA34" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AB34" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AC34" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD34" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="AE34" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AF34" t="s" s="2">
+      <c r="AE34" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AF34" t="s" s="5">
         <v>38</v>
       </c>
       <c r="AG34" t="s" s="0">
@@ -3900,94 +3900,94 @@
         <v>36</v>
       </c>
       <c r="C35" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E35" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="F35" t="s" s="1">
-        <v>35</v>
+      <c r="E35" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F35" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="G35" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="I35" t="s" s="5">
+        <v>39</v>
+      </c>
+      <c r="H35" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="I35" t="s" s="4">
         <v>39</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K35" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="L35" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="M35" t="s" s="1">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="M35" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="N35" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O35" t="s" s="1">
         <v>35</v>
       </c>
       <c r="P35" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Q35" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="R35" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="S35" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="Q35" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="R35" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S35" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="T35" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="U35" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="V35" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X35" t="s" s="5">
-        <v>39</v>
+        <v>39</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="V35" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="W35" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="X35" t="s" s="1">
+        <v>35</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z35" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA35" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AB35" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AC35" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD35" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AE35" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AG35" t="s" s="0">
         <v>40</v>
@@ -4004,94 +4004,94 @@
         <v>36</v>
       </c>
       <c r="C36" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s" s="1">
         <v>35</v>
       </c>
-      <c r="E36" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="F36" t="s" s="1">
-        <v>35</v>
+      <c r="E36" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="F36" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="G36" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I36" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K36" t="s" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L36" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M36" t="s" s="1">
         <v>35</v>
       </c>
       <c r="N36" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O36" t="s" s="1">
         <v>35</v>
       </c>
       <c r="P36" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Q36" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="R36" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="S36" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="Q36" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="R36" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="S36" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="T36" t="s" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V36" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="X36" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="Y36" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="Z36" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB36" t="s" s="5">
-        <v>39</v>
-      </c>
-      <c r="AC36" t="s" s="4">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="W36" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="X36" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="Z36" t="s" s="5">
+        <v>38</v>
+      </c>
+      <c r="AA36" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC36" t="s" s="5">
+        <v>38</v>
       </c>
       <c r="AD36" t="s" s="1">
         <v>35</v>
       </c>
       <c r="AE36" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="AF36" t="s" s="1">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>37</v>
       </c>
       <c r="AG36" t="s" s="0">
         <v>40</v>
